--- a/AAII_Financials/Yearly/CVLT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CVLT_YR_FIN.xlsx
@@ -1008,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>32900</v>
+        <v>34700</v>
       </c>
       <c r="E14" s="3">
         <v>14600</v>
@@ -1128,7 +1128,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1076800</v>
+        <v>1075000</v>
       </c>
       <c r="E17" s="3">
         <v>906900</v>
@@ -1179,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>106900</v>
+        <v>108700</v>
       </c>
       <c r="E18" s="3">
         <v>88700</v>
@@ -1302,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>117400</v>
+        <v>119200</v>
       </c>
       <c r="E21" s="3">
         <v>98500</v>
